--- a/posicao.xlsx
+++ b/posicao.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="193">
   <si>
     <t xml:space="preserve">Produto</t>
   </si>
@@ -61,217 +61,244 @@
     <t xml:space="preserve">Valor Atualizado</t>
   </si>
   <si>
+    <t xml:space="preserve">ABEV3 - AMBEV S.A.                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XP INVESTIMENTOS CCTVM S/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14482086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABEV3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07526557000100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRABEVACNOR1 - 134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANCO BRADESCO S/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BBAS3 - BCO BRASIL S.A.                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BBAS3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00000000000191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRBBASACNOR3 - 336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANCO DO BRASIL S/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EGIE3 - ENGIE BRASIL ENERGIA S.A.                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EGIE3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02474103000119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BREGIEACNOR9 - 132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITAU CV S/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLRY3 - FLEURY S.A.                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLRY3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60840055000131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRFLRYACNOR5 - 143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYPE3 - HYPERA S.A.                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYPE3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02932074000191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRHYPEACNOR0 - 151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITSA4 - ITAUSA S.A.                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITSA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61532644000115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRITSAACNPR7 - 457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KLBN11 - KLABIN S.A.                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KLBN11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89637490000145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRKLBNCDAM18 - 151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEVE3 - MAHLE-METAL LEVE S.A.                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEVE3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60476884000187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRLEVEACNOR2 - 202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAEE11 - TRANSMISSORA ALIANÇA DE ENERGIA ELÉTRICA S.A.     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAEE11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07859971000130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRTAEECDAM10 - 153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BTG PACTUAL SERVICOS FINANCEIROS S.A. DTVM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIP6 - UNIPAR CARBOCLORO S.A.                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIP6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33958695000178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRUNIPACNPB8 - 210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PNB</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natureza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Número de Contrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modalidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquidação antecipada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taxa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comissão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data de registro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data de vencimento</t>
+  </si>
+  <si>
     <t xml:space="preserve">B3SA3 - B3 S.A. - BRASIL, BOLSA, BALCÃO                   </t>
   </si>
   <si>
-    <t xml:space="preserve">XP INVESTIMENTOS CCTVM S/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14482086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B3SA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09346601000125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRB3SAACNOR6 - 140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BANCO BRADESCO S/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BBAS3 - BCO BRASIL S.A.                                   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BBAS3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">00000000000191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRBBASACNOR3 - 336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BANCO DO BRASIL S/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EGIE3 - ENGIE BRASIL ENERGIA S.A.                         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">EGIE3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02474103000119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BREGIEACNOR9 - 132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITAU CV S/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLRY3 - FLEURY S.A.                                       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLRY3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60840055000131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRFLRYACNOR5 - 143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYPE3 - HYPERA S.A.                                       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYPE3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02932074000191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRHYPEACNOR0 - 150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITSA4 - ITAUSA S.A.                                       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITSA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61532644000115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRITSAACNPR7 - 457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KLBN11 - KLABIN S.A.                                       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">KLBN11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89637490000145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRKLBNCDAM18 - 151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEVE3 - MAHLE-METAL LEVE S.A.                             </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEVE3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60476884000187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRLEVEACNOR2 - 202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAEE11 - TRANSMISSORA ALIANÇA DE ENERGIA ELÉTRICA S.A.     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAEE11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07859971000130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRTAEECDAM10 - 153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BTG PACTUAL SERVICOS FINANCEIROS S.A. DTVM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIP6 - UNIPAR CARBOCLORO S.A.                            </t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIP6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33958695000178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRUNIPACNPB8 - 210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PNB</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natureza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de Contrato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modalidade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liquidação antecipada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taxa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comissão</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data de registro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data de vencimento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABEV3 - AMBEV S.A.                                        </t>
-  </si>
-  <si>
     <t xml:space="preserve">Doador</t>
   </si>
   <si>
-    <t xml:space="preserve">2026031100923192280001-2</t>
+    <t xml:space="preserve">2026033000999303210001-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BBSE3 - BB SEGURIDADE PARTICIPAÇÕES S.A.                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026031100960399720001-2</t>
   </si>
   <si>
     <t xml:space="preserve">Registro</t>
   </si>
   <si>
-    <t xml:space="preserve">SIM</t>
-  </si>
-  <si>
     <t xml:space="preserve">11/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">13/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">BBSE3 - BB SEGURIDADE PARTICIPAÇÕES S.A.                  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026031100960399720001-2</t>
+    <t xml:space="preserve">2026032700997950810001-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026032600997242220001-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">PETR4 - PETROLEO BRASILEIRO S.A. PETROBRAS                </t>
@@ -280,9 +307,6 @@
     <t xml:space="preserve">2026031100921679210001-2</t>
   </si>
   <si>
-    <t xml:space="preserve">D1</t>
-  </si>
-  <si>
     <t xml:space="preserve">VALE3 - VALE S.A.                                         </t>
   </si>
   <si>
@@ -340,7 +364,7 @@
     <t xml:space="preserve">11728688000147</t>
   </si>
   <si>
-    <t xml:space="preserve">BRHGLGCTF004 - 294</t>
+    <t xml:space="preserve">BRHGLGCTF004 - 295</t>
   </si>
   <si>
     <t xml:space="preserve">BANCO GENIAL S.A</t>
@@ -355,7 +379,7 @@
     <t xml:space="preserve">29641226000153</t>
   </si>
   <si>
-    <t xml:space="preserve">BRHGRUCTF002 - 198</t>
+    <t xml:space="preserve">BRHGRUCTF002 - 199</t>
   </si>
   <si>
     <t xml:space="preserve">KNRI11 - KINEA RENDA IMOBILIÁRIA FDO INV IMOB RESP LIM     </t>
@@ -367,7 +391,7 @@
     <t xml:space="preserve">12005956000165</t>
   </si>
   <si>
-    <t xml:space="preserve">BRKNRICTF007 - 285</t>
+    <t xml:space="preserve">BRKNRICTF007 - 286</t>
   </si>
   <si>
     <t xml:space="preserve">LVBI11 - FDO INV IMOB - VBI LOGÍSTICO RESP LIM             </t>
@@ -379,7 +403,7 @@
     <t xml:space="preserve">30629603000118</t>
   </si>
   <si>
-    <t xml:space="preserve">BRLVBICTF002 - 190</t>
+    <t xml:space="preserve">BRLVBICTF002 - 191</t>
   </si>
   <si>
     <t xml:space="preserve">TRXF11 - TRX REAL ESTATE FDO. INV. IMOB. - FII RESP LIM    </t>
@@ -391,7 +415,7 @@
     <t xml:space="preserve">28548288000152</t>
   </si>
   <si>
-    <t xml:space="preserve">BRTRXFCTF003 - 187</t>
+    <t xml:space="preserve">BRTRXFCTF003 - 188</t>
   </si>
   <si>
     <t xml:space="preserve">BRL TRUST DTVM S/A</t>
@@ -418,7 +442,7 @@
     <t xml:space="preserve">26502794000185</t>
   </si>
   <si>
-    <t xml:space="preserve">BRXPLGCTF002 - 201</t>
+    <t xml:space="preserve">BRXPLGCTF002 - 202</t>
   </si>
   <si>
     <t xml:space="preserve">OLIVEIRA TRUST DTVM  S/A</t>
@@ -508,13 +532,13 @@
     <t xml:space="preserve">P470</t>
   </si>
   <si>
-    <t xml:space="preserve">Opção de Venda - PETRQ338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PETRQ338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q338</t>
+    <t xml:space="preserve">Opção de Venda - RADLQ216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RADLQ216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q216</t>
   </si>
   <si>
     <t xml:space="preserve">Opção de Venda - VALEQ764</t>
@@ -727,10 +751,10 @@
         <v>21</v>
       </c>
       <c r="I2" s="5">
-        <v>57</v>
+        <v>200</v>
       </c>
       <c r="J2" s="5">
-        <v>57</v>
+        <v>200</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>22</v>
@@ -739,10 +763,10 @@
         <v>22</v>
       </c>
       <c r="M2" s="4">
-        <v>17.38</v>
+        <v>15.28</v>
       </c>
       <c r="N2" s="4">
-        <v>990.66</v>
+        <v>3056</v>
       </c>
     </row>
     <row r="3">
@@ -783,10 +807,10 @@
         <v>22</v>
       </c>
       <c r="M3" s="4">
-        <v>23.65</v>
+        <v>23.39</v>
       </c>
       <c r="N3" s="4">
-        <v>9885.7</v>
+        <v>9777.02</v>
       </c>
     </row>
     <row r="4">
@@ -827,10 +851,10 @@
         <v>22</v>
       </c>
       <c r="M4" s="4">
-        <v>31.71</v>
+        <v>33.28</v>
       </c>
       <c r="N4" s="4">
-        <v>4439.4</v>
+        <v>4659.2</v>
       </c>
     </row>
     <row r="5">
@@ -871,10 +895,10 @@
         <v>22</v>
       </c>
       <c r="M5" s="4">
-        <v>15.4</v>
+        <v>15.88</v>
       </c>
       <c r="N5" s="4">
-        <v>2356.2</v>
+        <v>2429.64</v>
       </c>
     </row>
     <row r="6">
@@ -903,10 +927,10 @@
         <v>21</v>
       </c>
       <c r="I6" s="5">
-        <v>400</v>
+        <v>11</v>
       </c>
       <c r="J6" s="5">
-        <v>400</v>
+        <v>11</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>22</v>
@@ -915,10 +939,10 @@
         <v>22</v>
       </c>
       <c r="M6" s="4">
-        <v>22.9</v>
+        <v>22.99</v>
       </c>
       <c r="N6" s="4">
-        <v>9160</v>
+        <v>252.89</v>
       </c>
     </row>
     <row r="7">
@@ -959,10 +983,10 @@
         <v>22</v>
       </c>
       <c r="M7" s="4">
-        <v>13.5</v>
+        <v>13.92</v>
       </c>
       <c r="N7" s="4">
-        <v>3483</v>
+        <v>3591.36</v>
       </c>
     </row>
     <row r="8">
@@ -1003,10 +1027,10 @@
         <v>22</v>
       </c>
       <c r="M8" s="4">
-        <v>19.14</v>
+        <v>19.32</v>
       </c>
       <c r="N8" s="4">
-        <v>9608.28</v>
+        <v>9698.64</v>
       </c>
     </row>
     <row r="9">
@@ -1091,10 +1115,10 @@
         <v>22</v>
       </c>
       <c r="M10" s="4">
-        <v>41.99</v>
+        <v>42.83</v>
       </c>
       <c r="N10" s="4">
-        <v>2477.41</v>
+        <v>2526.97</v>
       </c>
     </row>
     <row r="11">
@@ -1135,10 +1159,10 @@
         <v>22</v>
       </c>
       <c r="M11" s="4">
-        <v>57.55</v>
+        <v>60.51</v>
       </c>
       <c r="N11" s="4">
-        <v>1956.7</v>
+        <v>2057.34</v>
       </c>
     </row>
     <row r="12">
@@ -1231,7 +1255,7 @@
         <v>65</v>
       </c>
       <c r="N14" s="4">
-        <v>47869.35</v>
+        <v>41561.06</v>
       </c>
     </row>
   </sheetData>
@@ -1327,7 +1351,7 @@
         <v>80</v>
       </c>
       <c r="H2" s="5">
-        <v>0.28</v>
+        <v>0.07</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>22</v>
@@ -1339,13 +1363,13 @@
         <v>82</v>
       </c>
       <c r="L2" s="5">
-        <v>200</v>
+        <v>57</v>
       </c>
       <c r="M2" s="4">
-        <v>14.7</v>
+        <v>18.59</v>
       </c>
       <c r="N2" s="4">
-        <v>2940</v>
+        <v>1059.63</v>
       </c>
     </row>
     <row r="3">
@@ -1362,7 +1386,7 @@
         <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F3" t="s">
         <v>80</v>
@@ -1377,24 +1401,24 @@
         <v>22</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="L3" s="5">
         <v>100</v>
       </c>
       <c r="M3" s="4">
-        <v>34.46</v>
+        <v>35.43</v>
       </c>
       <c r="N3" s="4">
-        <v>3446</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
@@ -1403,10 +1427,10 @@
         <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F4" t="s">
         <v>80</v>
@@ -1415,30 +1439,30 @@
         <v>80</v>
       </c>
       <c r="H4" s="5">
-        <v>0.8</v>
+        <v>0.04</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>22</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L4" s="5">
-        <v>151</v>
+        <v>378</v>
       </c>
       <c r="M4" s="4">
-        <v>47.27</v>
+        <v>22.99</v>
       </c>
       <c r="N4" s="4">
-        <v>7137.77</v>
+        <v>8690.22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
@@ -1447,10 +1471,10 @@
         <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F5" t="s">
         <v>80</v>
@@ -1459,118 +1483,206 @@
         <v>80</v>
       </c>
       <c r="H5" s="5">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>22</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L5" s="5">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="M5" s="4">
-        <v>78.1</v>
+        <v>22.99</v>
       </c>
       <c r="N5" s="4">
-        <v>5701.3</v>
+        <v>252.89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>94</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="L6" s="5">
+        <v>151</v>
+      </c>
+      <c r="M6" s="4">
+        <v>48.15</v>
+      </c>
+      <c r="N6" s="4">
+        <v>7270.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I7" t="s">
-        <v>65</v>
-      </c>
-      <c r="J7" t="s">
-        <v>65</v>
-      </c>
-      <c r="K7" t="s">
-        <v>65</v>
-      </c>
-      <c r="L7" t="s">
-        <v>65</v>
-      </c>
-      <c r="M7" t="s">
-        <v>65</v>
-      </c>
-      <c r="N7" t="s">
-        <v>66</v>
+        <v>80</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.06</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L7" s="5">
+        <v>73</v>
+      </c>
+      <c r="M7" s="4">
+        <v>83.55</v>
+      </c>
+      <c r="N7" s="4">
+        <v>6099.15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
         <v>65</v>
       </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8" t="s">
-        <v>65</v>
-      </c>
-      <c r="H8" t="s">
-        <v>65</v>
-      </c>
-      <c r="I8" t="s">
-        <v>65</v>
-      </c>
-      <c r="J8" t="s">
-        <v>65</v>
-      </c>
-      <c r="K8" t="s">
-        <v>65</v>
-      </c>
-      <c r="L8" t="s">
-        <v>65</v>
-      </c>
-      <c r="M8" t="s">
-        <v>65</v>
-      </c>
-      <c r="N8" s="4">
-        <v>19225.07</v>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" t="s">
+        <v>65</v>
+      </c>
+      <c r="L9" t="s">
+        <v>65</v>
+      </c>
+      <c r="M9" t="s">
+        <v>65</v>
+      </c>
+      <c r="N9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10" t="s">
+        <v>65</v>
+      </c>
+      <c r="K10" t="s">
+        <v>65</v>
+      </c>
+      <c r="L10" t="s">
+        <v>65</v>
+      </c>
+      <c r="M10" t="s">
+        <v>65</v>
+      </c>
+      <c r="N10" s="4">
+        <v>26915.54</v>
       </c>
     </row>
   </sheetData>
@@ -1595,7 +1707,7 @@
     <col min="10" max="10" width="29.19140625" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="11" max="11" width="12.19140625" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="12" max="12" width="31.33203125" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="31.33203125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="30.33203125" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1612,7 +1724,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
@@ -1641,7 +1753,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
@@ -1650,16 +1762,16 @@
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H2" s="5">
         <v>5</v>
@@ -1674,10 +1786,10 @@
         <v>22</v>
       </c>
       <c r="L2" s="4">
-        <v>103.17</v>
+        <v>101.56</v>
       </c>
       <c r="M2" s="4">
-        <v>515.85</v>
+        <v>507.8</v>
       </c>
     </row>
     <row r="3">
@@ -1764,7 +1876,7 @@
         <v>65</v>
       </c>
       <c r="M5" s="4">
-        <v>515.85</v>
+        <v>507.8</v>
       </c>
     </row>
   </sheetData>
@@ -1790,7 +1902,7 @@
     <col min="11" max="11" width="29.19140625" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="12" max="12" width="12.19140625" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="13" max="13" width="31.33203125" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="14" width="33.4765625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="14" width="31.33203125" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1807,7 +1919,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
@@ -1816,7 +1928,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>8</v>
@@ -1839,7 +1951,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
@@ -1848,16 +1960,16 @@
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="F2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="G2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H2" t="s">
         <v>59</v>
@@ -1875,15 +1987,15 @@
         <v>22</v>
       </c>
       <c r="M2" s="4">
-        <v>103.8</v>
+        <v>104.01</v>
       </c>
       <c r="N2" s="4">
-        <v>8200.2</v>
+        <v>8216.79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -1892,19 +2004,19 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="G3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H3" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="I3" s="5">
         <v>41</v>
@@ -1919,15 +2031,15 @@
         <v>22</v>
       </c>
       <c r="M3" s="4">
-        <v>156</v>
+        <v>156.16</v>
       </c>
       <c r="N3" s="4">
-        <v>6396</v>
+        <v>6402.56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
@@ -1936,19 +2048,19 @@
         <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G4" t="s">
         <v>111</v>
       </c>
-      <c r="F4" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" t="s">
-        <v>103</v>
-      </c>
       <c r="H4" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="I4" s="5">
         <v>32</v>
@@ -1963,15 +2075,15 @@
         <v>22</v>
       </c>
       <c r="M4" s="4">
-        <v>128.06</v>
+        <v>129</v>
       </c>
       <c r="N4" s="4">
-        <v>4097.92</v>
+        <v>4128</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
@@ -1980,16 +2092,16 @@
         <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="F5" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="G5" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H5" t="s">
         <v>32</v>
@@ -2007,15 +2119,15 @@
         <v>22</v>
       </c>
       <c r="M5" s="4">
-        <v>164.13</v>
+        <v>166.79</v>
       </c>
       <c r="N5" s="4">
-        <v>1969.56</v>
+        <v>2001.48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
@@ -2024,16 +2136,16 @@
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="F6" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G6" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H6" t="s">
         <v>59</v>
@@ -2051,15 +2163,15 @@
         <v>22</v>
       </c>
       <c r="M6" s="4">
-        <v>109.19</v>
+        <v>108.56</v>
       </c>
       <c r="N6" s="4">
-        <v>6114.64</v>
+        <v>6079.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
@@ -2068,19 +2180,19 @@
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="F7" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="G7" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H7" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="I7" s="5">
         <v>72</v>
@@ -2095,15 +2207,15 @@
         <v>22</v>
       </c>
       <c r="M7" s="4">
-        <v>91.67</v>
+        <v>91.46</v>
       </c>
       <c r="N7" s="4">
-        <v>6600.24</v>
+        <v>6585.12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
@@ -2112,16 +2224,16 @@
         <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E8" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F8" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G8" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H8" t="s">
         <v>59</v>
@@ -2139,15 +2251,15 @@
         <v>22</v>
       </c>
       <c r="M8" s="4">
-        <v>79.61</v>
+        <v>80.97</v>
       </c>
       <c r="N8" s="4">
-        <v>4856.21</v>
+        <v>4939.17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
@@ -2156,19 +2268,19 @@
         <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E9" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="F9" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="G9" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H9" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="I9" s="5">
         <v>79</v>
@@ -2183,15 +2295,15 @@
         <v>22</v>
       </c>
       <c r="M9" s="4">
-        <v>101.14</v>
+        <v>100.59</v>
       </c>
       <c r="N9" s="4">
-        <v>7990.06</v>
+        <v>7946.61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
@@ -2200,16 +2312,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E10" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F10" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G10" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H10" t="s">
         <v>59</v>
@@ -2227,10 +2339,10 @@
         <v>22</v>
       </c>
       <c r="M10" s="4">
-        <v>107.6</v>
+        <v>109.31</v>
       </c>
       <c r="N10" s="4">
-        <v>6563.6</v>
+        <v>6667.91</v>
       </c>
     </row>
     <row r="11">
@@ -2323,7 +2435,7 @@
         <v>65</v>
       </c>
       <c r="N13" s="4">
-        <v>52788.43</v>
+        <v>52967</v>
       </c>
     </row>
   </sheetData>
@@ -2336,7 +2448,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29.4765625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="29.6171875" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="31.90625" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="3" max="3" width="19.046875" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="4" max="4" width="13.046875" bestFit="1" customWidth="1" collapsed="1"/>
@@ -2364,19 +2476,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>8</v>
@@ -2391,22 +2503,22 @@
         <v>11</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>13</v>
@@ -2414,25 +2526,25 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="G2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="H2" s="5">
         <v>200</v>
@@ -2456,7 +2568,7 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="P2" s="4">
         <v>24.02</v>
@@ -2465,30 +2577,30 @@
         <v>0</v>
       </c>
       <c r="R2" s="4">
-        <v>170</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="D3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="F3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="G3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="H3" s="5">
         <v>200</v>
@@ -2512,7 +2624,7 @@
         <v>22</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="P3" s="4">
         <v>34.43</v>
@@ -2521,30 +2633,30 @@
         <v>0</v>
       </c>
       <c r="R3" s="4">
-        <v>150</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="D4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E4" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G4" t="s">
         <v>162</v>
-      </c>
-      <c r="G4" t="s">
-        <v>154</v>
       </c>
       <c r="H4" s="5">
         <v>200</v>
@@ -2568,7 +2680,7 @@
         <v>22</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="P4" s="4">
         <v>31.24</v>
@@ -2577,30 +2689,30 @@
         <v>0</v>
       </c>
       <c r="R4" s="4">
-        <v>124</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="D5" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E5" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="F5" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G5" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="H5" s="5">
         <v>200</v>
@@ -2624,39 +2736,39 @@
         <v>22</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="P5" s="4">
-        <v>33</v>
+        <v>21.69</v>
       </c>
       <c r="Q5" s="4">
         <v>0</v>
       </c>
       <c r="R5" s="4">
-        <v>16</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E6" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="F6" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="G6" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="H6" s="5">
         <v>100</v>
@@ -2680,7 +2792,7 @@
         <v>22</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="P6" s="4">
         <v>76.4</v>
@@ -2689,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="R6" s="4">
-        <v>233</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -2806,7 +2918,7 @@
         <v>65</v>
       </c>
       <c r="R9" s="4">
-        <v>693</v>
+        <v>593</v>
       </c>
     </row>
   </sheetData>
@@ -2829,7 +2941,7 @@
     <col min="8" max="8" width="29.19140625" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="9" max="9" width="12.19140625" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="10" max="10" width="33.4765625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="33.4765625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="31.33203125" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="12" max="12" width="33.4765625" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="13" max="13" width="33.4765625" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
@@ -2842,13 +2954,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>8</v>
@@ -2863,13 +2975,13 @@
         <v>11</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>13</v>
@@ -2877,19 +2989,19 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D2" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F2" s="5">
         <v>4.88</v>
@@ -2907,30 +3019,30 @@
         <v>20960.95</v>
       </c>
       <c r="K2" s="4">
-        <v>20652.24</v>
+        <v>20991</v>
       </c>
       <c r="L2" s="4">
-        <v>20624.73</v>
+        <v>20930.16</v>
       </c>
       <c r="M2" s="4">
-        <v>20652.24</v>
+        <v>20991</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D3" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="F3" s="5">
         <v>3.12</v>
@@ -2948,30 +3060,30 @@
         <v>1524.49</v>
       </c>
       <c r="K3" s="4">
-        <v>1659.18</v>
+        <v>1684.67</v>
       </c>
       <c r="L3" s="4">
-        <v>1629.62</v>
+        <v>1654.58</v>
       </c>
       <c r="M3" s="4">
-        <v>1659.18</v>
+        <v>1684.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D4" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="F4" s="5">
         <v>8.79</v>
@@ -2989,13 +3101,13 @@
         <v>6995.78</v>
       </c>
       <c r="K4" s="4">
-        <v>7227.57</v>
+        <v>7325.05</v>
       </c>
       <c r="L4" s="4">
-        <v>7183.77</v>
+        <v>7263.83</v>
       </c>
       <c r="M4" s="4">
-        <v>7227.57</v>
+        <v>7325.05</v>
       </c>
     </row>
     <row r="5">
@@ -3082,7 +3194,7 @@
         <v>65</v>
       </c>
       <c r="M7" s="4">
-        <v>29538.99</v>
+        <v>30000.72</v>
       </c>
     </row>
   </sheetData>
